--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$51</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="483">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T07:30:07+05:30</t>
+    <t>2026-05-16T10:04:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -701,11 +701,12 @@
 </t>
   </si>
   <si>
-    <t>High-level category classification for the requested service</t>
-  </si>
-  <si>
-    <t>Categorizes the requested service into a standardized
-high-level clinical service domain.</t>
+    <t>Operational procedure/service categories</t>
+  </si>
+  <si>
+    <t>Broad and optional subcategory classifications used
+for workflow, routing, analytics, and operational
+grouping of ServiceRequest resources.</t>
   </si>
   <si>
     <t>There may be multiple axis of categorization depending on the context or use case for retrieving or displaying the resource.  The level of granularity is defined by the category concepts in the value set.</t>
@@ -714,7 +715,13 @@
     <t>Used for filtering what service request are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://314e.com/fhir/ValueSet/servicerequest-category-314e</t>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Classification of the requested service.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -748,6 +755,38 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-servicerequest-category</t>
   </si>
   <si>
+    <t>ServiceRequest.category:broadCategory</t>
+  </si>
+  <si>
+    <t>broadCategory</t>
+  </si>
+  <si>
+    <t>Required broad procedure/service category</t>
+  </si>
+  <si>
+    <t>Top-level operational classification of the requested
+service or procedure.</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/ValueSet/procedure-category-broad-314e</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category:subCategory</t>
+  </si>
+  <si>
+    <t>subCategory</t>
+  </si>
+  <si>
+    <t>Optional detailed subcategory</t>
+  </si>
+  <si>
+    <t>More granular operational sub-classification of the
+requested service or procedure.</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/ValueSet/procedure-category-subcategory-314e</t>
+  </si>
+  <si>
     <t>ServiceRequest.priority</t>
   </si>
   <si>
@@ -973,9 +1012,6 @@
   </si>
   <si>
     <t>For information from the medical record intended to support the delivery of the requested services, use the `supportingInformation` element.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Codified order entry details which are based on order context.</t>
@@ -1815,12 +1851,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO49"/>
+  <dimension ref="A1:AO51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.640625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="30.87890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.12890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.8671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="38.546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -4035,24 +4071,26 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>216</v>
@@ -4073,10 +4111,10 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>215</v>
@@ -4087,13 +4125,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>216</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>20</v>
@@ -4118,10 +4156,10 @@
         <v>217</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>220</v>
@@ -4155,10 +4193,10 @@
         <v>199</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -4194,10 +4232,10 @@
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>215</v>
@@ -4206,26 +4244,28 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
@@ -4234,22 +4274,24 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>110</v>
+        <v>217</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q21" t="s" s="2">
-        <v>236</v>
-      </c>
+      <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
         <v>20</v>
       </c>
@@ -4271,11 +4313,9 @@
       <c r="X21" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="Y21" t="s" s="2">
-        <v>237</v>
-      </c>
+      <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4293,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -4308,29 +4348,31 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>239</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="B22" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AN21" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" hidden="true">
-      <c r="A22" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>20</v>
       </c>
@@ -4342,62 +4384,58 @@
         <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="P22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="Y22" s="2"/>
+      <c r="Z22" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="P22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q22" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="R22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
       </c>
@@ -4414,13 +4452,13 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
@@ -4429,41 +4467,41 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
@@ -4472,22 +4510,22 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>217</v>
+        <v>110</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q23" s="2"/>
+      <c r="Q23" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="R23" t="s" s="2">
         <v>20</v>
       </c>
@@ -4507,11 +4545,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4529,7 +4569,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4538,33 +4578,33 @@
         <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4581,26 +4621,32 @@
         <v>20</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q24" s="2"/>
+      <c r="Q24" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="R24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4644,7 +4690,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4656,16 +4702,16 @@
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>20</v>
+        <v>262</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
@@ -4674,44 +4720,44 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>135</v>
+        <v>265</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>136</v>
+        <v>217</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>137</v>
+        <v>266</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>139</v>
+        <v>268</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4737,70 +4783,66 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>20</v>
+        <v>270</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AC25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AD25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AF25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AG25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AO25" t="s" s="2">
-        <v>20</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C26" t="s" s="2">
         <v>277</v>
       </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>20</v>
       </c>
@@ -4829,9 +4871,7 @@
       <c r="M26" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N26" t="s" s="2">
-        <v>281</v>
-      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4880,28 +4920,28 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -4912,14 +4952,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4935,23 +4975,21 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>285</v>
+        <v>136</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>286</v>
+        <v>137</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
       </c>
@@ -4987,19 +5025,19 @@
         <v>20</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>20</v>
+        <v>286</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5011,16 +5049,16 @@
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>20</v>
@@ -5031,12 +5069,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>20</v>
       </c>
@@ -5054,23 +5094,21 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -5118,28 +5156,28 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>20</v>
+        <v>271</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>20</v>
@@ -5150,14 +5188,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>302</v>
+        <v>20</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5176,18 +5214,20 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>217</v>
+        <v>297</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -5211,13 +5251,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>308</v>
+        <v>20</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5235,7 +5275,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5244,7 +5284,7 @@
         <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>309</v>
+        <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>102</v>
@@ -5253,24 +5293,24 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>262</v>
+        <v>304</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5293,17 +5333,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>312</v>
+        <v>278</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="O30" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5352,7 +5394,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5370,10 +5412,10 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>20</v>
@@ -5382,26 +5424,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>20</v>
@@ -5410,15 +5452,17 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>318</v>
+        <v>217</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5443,13 +5487,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>20</v>
+        <v>319</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5467,46 +5511,46 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AM31" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>326</v>
-      </c>
       <c r="B32" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>327</v>
+        <v>20</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5516,7 +5560,7 @@
         <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>20</v>
@@ -5525,16 +5569,18 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5582,7 +5628,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5597,35 +5643,35 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>334</v>
+        <v>20</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>335</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>337</v>
+        <v>20</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>90</v>
@@ -5640,13 +5686,13 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5697,10 +5743,10 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>90</v>
@@ -5712,31 +5758,31 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>20</v>
+        <v>338</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5746,7 +5792,7 @@
         <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>20</v>
@@ -5755,13 +5801,13 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5788,13 +5834,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>351</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5812,7 +5858,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5827,31 +5873,31 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>20</v>
+        <v>342</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>20</v>
+        <v>343</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>20</v>
+        <v>345</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5870,13 +5916,13 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5927,7 +5973,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5942,31 +5988,31 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>365</v>
+        <v>20</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5976,7 +6022,7 @@
         <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>20</v>
@@ -5985,17 +6031,15 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6020,13 +6064,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>20</v>
+        <v>361</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>20</v>
+        <v>362</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6044,7 +6088,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6059,31 +6103,31 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>370</v>
+        <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>371</v>
+        <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6093,7 +6137,7 @@
         <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
@@ -6102,17 +6146,15 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>217</v>
+        <v>367</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6137,13 +6179,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -6161,7 +6203,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6176,41 +6218,41 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>20</v>
+        <v>374</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>20</v>
@@ -6219,16 +6261,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6278,13 +6320,13 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
@@ -6293,38 +6335,38 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>20</v>
+        <v>387</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6339,12 +6381,14 @@
         <v>217</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6369,13 +6413,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>306</v>
+        <v>222</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6393,13 +6437,13 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
@@ -6408,16 +6452,16 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>20</v>
+        <v>394</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -6425,14 +6469,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>20</v>
+        <v>398</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6451,15 +6495,17 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L40" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6508,7 +6554,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6523,16 +6569,16 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>20</v>
+        <v>403</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>20</v>
+        <v>404</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -6540,10 +6586,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6569,14 +6615,12 @@
         <v>217</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N41" t="s" s="2">
         <v>408</v>
       </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6601,11 +6645,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="Z41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6623,7 +6669,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6638,16 +6684,16 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>410</v>
+        <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AM41" t="s" s="2">
-        <v>412</v>
-      </c>
       <c r="AN41" t="s" s="2">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -6655,10 +6701,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6681,17 +6727,15 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6740,7 +6784,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6755,16 +6799,16 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>419</v>
+        <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>420</v>
+        <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -6772,10 +6816,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6795,18 +6839,20 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>423</v>
+        <v>217</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6831,13 +6877,11 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6855,7 +6899,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6870,16 +6914,16 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>20</v>
+        <v>424</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -6887,14 +6931,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>430</v>
+        <v>20</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6910,19 +6954,19 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6972,7 +7016,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6987,16 +7031,16 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>20</v>
+        <v>424</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -7004,10 +7048,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7027,20 +7071,18 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7089,7 +7131,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7104,13 +7146,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>20</v>
+        <v>437</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
@@ -7121,14 +7163,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7144,23 +7186,21 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>217</v>
+        <v>442</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7184,13 +7224,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>451</v>
+        <v>20</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>452</v>
+        <v>20</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7208,7 +7248,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7223,27 +7263,27 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>20</v>
+        <v>446</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>454</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7263,18 +7303,20 @@
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>51</v>
+        <v>451</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7323,7 +7365,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7338,38 +7380,38 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>458</v>
+        <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>310</v>
+        <v>454</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>460</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>20</v>
+        <v>457</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7381,16 +7423,20 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>266</v>
+        <v>217</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7414,13 +7460,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>20</v>
+        <v>462</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>20</v>
+        <v>463</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7438,13 +7484,13 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
@@ -7456,7 +7502,7 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>310</v>
+        <v>454</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>464</v>
@@ -7465,15 +7511,15 @@
         <v>20</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>20</v>
+        <v>465</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7496,17 +7542,15 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>467</v>
+        <v>51</v>
       </c>
       <c r="M49" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="N49" t="s" s="2">
-        <v>469</v>
-      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7555,7 +7599,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7570,23 +7614,255 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO49" t="s" s="2">
+      <c r="AM51" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO49">
+  <autoFilter ref="A1:AO51">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7596,7 +7872,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI48">
+  <conditionalFormatting sqref="A2:AI50">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T10:04:42+05:30</t>
+    <t>2026-05-16T10:41:11+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T10:41:11+05:30</t>
+    <t>2026-05-16T12:18:43+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T12:18:43+05:30</t>
+    <t>2026-05-16T12:58:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T12:58:39+05:30</t>
+    <t>2026-05-16T13:10:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T13:10:22+05:30</t>
+    <t>2026-05-16T16:45:26+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T16:45:26+05:30</t>
+    <t>2026-05-17T00:25:02+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$67</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2517" uniqueCount="570">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-17T00:25:02+05:30</t>
+    <t>2026-05-19T06:46:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -483,32 +483,282 @@
     <t>ServiceRequest.identifier</t>
   </si>
   <si>
+    <t xml:space="preserve">Identifier {http://314e.com/fhir/ig/StructureDefinition/identifier-314e}
+</t>
+  </si>
+  <si>
+    <t>Identifiers assigned to this order</t>
+  </si>
+  <si>
+    <t>Identifiers assigned to this order instance by the orderer and/or the receiver and/or order fulfiller.</t>
+  </si>
+  <si>
+    <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 v2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 v2).  For further discussion and examples see the resource notes section below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Request.identifier</t>
+  </si>
+  <si>
+    <t>ORC.2, ORC.3, RF1-6 / RF1-11,</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>ClinicalStatement.identifier</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:internalIdentifier</t>
+  </si>
+  <si>
+    <t>internalIdentifier</t>
+  </si>
+  <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>Identifiers assigned to this order</t>
-  </si>
-  <si>
-    <t>Identifiers assigned to this order instance by the orderer and/or the receiver and/or order fulfiller.</t>
-  </si>
-  <si>
-    <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 v2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 v2).  For further discussion and examples see the resource notes section below.</t>
-  </si>
-  <si>
-    <t>Request.identifier</t>
-  </si>
-  <si>
-    <t>ORC.2, ORC.3, RF1-6 / RF1-11,</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>ClinicalStatement.identifier</t>
+    <t>Customer-specific internal identifier whose system SHALL follow the mandated 314e naming convention</t>
+  </si>
+  <si>
+    <t>Customer-specific or internally defined identifier
+used within local workflows, source systems,
+or operational environments.
+Identifier.system SHALL follow the naming convention:
+[customer]-[ehr]-[ResourceType]-[resource-subtype]-[eleMent]-[SourceSpecificString]-InternalIdentifier
+Example of Identifier.system for internal identifier:
+acme-cerner-ServiceRequest-imaging-identifier-AccessionNumber-InternalIdentifier</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:internalIdentifier.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:internalIdentifier.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:internalIdentifier.use</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:internalIdentifier.type</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:internalIdentifier.system</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:internalIdentifier.value</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:internalIdentifier.period</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:internalIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
   </si>
   <si>
     <t>ServiceRequest.instantiatesCanonical</t>
@@ -643,9 +893,6 @@
     <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, cancelled or suspended. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](http://hl7.org/fhir/R4/event.html) for general discussion) or using the [Task](http://hl7.org/fhir/R4/task.html) resource.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>The status of a service order.</t>
   </si>
   <si>
@@ -697,7 +944,7 @@
     <t>ServiceRequest.category</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
+    <t xml:space="preserve">CodeableConcept {http://314e.com/fhir/ig/StructureDefinition/codeableconcept-314e}
 </t>
   </si>
   <si>
@@ -724,13 +971,6 @@
     <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>RF1-5</t>
   </si>
   <si>
@@ -861,9 +1101,6 @@
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-procedure-code</t>
   </si>
   <si>
@@ -889,36 +1126,7 @@
     <t>ServiceRequest.code.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>ServiceRequest.code.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>ServiceRequest.code.extension:codeOptions</t>
@@ -1043,7 +1251,44 @@
     <t>When ordering a service the number of service items may need to be specified separately from the the service item.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>.quantity</t>
+  </si>
+  <si>
+    <t>ServiceRequest.quantity[x]:quantityQuantity</t>
+  </si>
+  <si>
+    <t>quantityQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity {http://314e.com/fhir/ig/StructureDefinition/quantity-314e}
+</t>
+  </si>
+  <si>
+    <t>ServiceRequest.quantity[x]:quantityRange</t>
+  </si>
+  <si>
+    <t>quantityRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range {http://314e.com/fhir/StructureDefinition/range-314e}
+</t>
+  </si>
+  <si>
+    <t>ServiceRequest.quantity[x]:quantityRatio</t>
+  </si>
+  <si>
+    <t>quantityRatio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio {http://314e.com/fhir/StructureDefinition/ratio-314e}
+</t>
   </si>
   <si>
     <t>ServiceRequest.subject</t>
@@ -1138,6 +1383,36 @@
     <t>Procedure.procedureSchedule</t>
   </si>
   <si>
+    <t>ServiceRequest.occurrence[x]:occurrenceDateTime</t>
+  </si>
+  <si>
+    <t>occurrenceDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime {http://314e.com/fhir/ig/StructureDefinition/datetime-314e}
+</t>
+  </si>
+  <si>
+    <t>ServiceRequest.occurrence[x]:occurrencePeriod</t>
+  </si>
+  <si>
+    <t>occurrencePeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period {http://314e.com/fhir/ig/StructureDefinition/period-314e}
+</t>
+  </si>
+  <si>
+    <t>ServiceRequest.occurrence[x]:occurrenceTiming</t>
+  </si>
+  <si>
+    <t>occurrenceTiming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timing {http://314e.com/fhir/ig/StructureDefinition/timing-314e}
+</t>
+  </si>
+  <si>
     <t>ServiceRequest.asNeeded[x]</t>
   </si>
   <si>
@@ -1163,14 +1438,16 @@
     <t>Proposal.prnReason.reason</t>
   </si>
   <si>
+    <t>ServiceRequest.asNeeded[x]:asNeededCodeableConcept</t>
+  </si>
+  <si>
+    <t>asNeededCodeableConcept</t>
+  </si>
+  <si>
     <t>ServiceRequest.authoredOn</t>
   </si>
   <si>
     <t xml:space="preserve">orderedOn
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
 </t>
   </si>
   <si>
@@ -1851,12 +2128,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO51"/>
+  <dimension ref="A1:AO67"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="36.640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="30.87890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.8671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="23.109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="38.546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -1873,7 +2150,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="34.80859375" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
@@ -3147,16 +3424,14 @@
         <v>20</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>147</v>
@@ -3174,29 +3449,31 @@
         <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
       </c>
@@ -3217,16 +3494,16 @@
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3276,7 +3553,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3291,24 +3568,24 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>165</v>
@@ -3322,7 +3599,7 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -3331,20 +3608,18 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N13" t="s" s="2">
         <v>168</v>
       </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3393,28 +3668,28 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>163</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>20</v>
@@ -3425,14 +3700,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3448,18 +3723,20 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N14" s="2"/>
+      <c r="N14" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3496,19 +3773,19 @@
         <v>20</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3520,16 +3797,16 @@
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>20</v>
@@ -3540,42 +3817,46 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>20</v>
       </c>
@@ -3599,13 +3880,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>20</v>
+        <v>185</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3623,13 +3904,13 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
@@ -3638,13 +3919,13 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>20</v>
@@ -3655,14 +3936,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3681,19 +3962,19 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3718,13 +3999,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3742,7 +4023,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3757,13 +4038,13 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>192</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>20</v>
@@ -3772,12 +4053,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3785,33 +4066,35 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3823,7 +4106,7 @@
         <v>20</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>20</v>
@@ -3835,13 +4118,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>201</v>
+        <v>20</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3859,10 +4142,10 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>90</v>
@@ -3874,27 +4157,27 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>206</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3902,31 +4185,31 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3940,7 +4223,7 @@
         <v>20</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>20</v>
@@ -3952,13 +4235,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>211</v>
+        <v>20</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -3976,10 +4259,10 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>90</v>
@@ -3991,16 +4274,16 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>133</v>
+        <v>217</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -4008,10 +4291,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4019,13 +4302,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G19" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G19" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H19" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
@@ -4034,20 +4317,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>20</v>
       </c>
@@ -4071,35 +4350,37 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>223</v>
+        <v>20</v>
       </c>
       <c r="Z19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AA19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AC19" s="2"/>
-      <c r="AD19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>216</v>
-      </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -4111,28 +4392,26 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" hidden="true">
+      <c r="A20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="B20" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AN19" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>230</v>
-      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>20</v>
       </c>
@@ -4141,10 +4420,10 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
@@ -4153,20 +4432,18 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="N20" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>221</v>
-      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
       </c>
@@ -4190,37 +4467,37 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="Z20" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>216</v>
-      </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
@@ -4232,40 +4509,38 @@
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C21" t="s" s="2">
         <v>236</v>
       </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
@@ -4274,20 +4549,18 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>20</v>
       </c>
@@ -4311,11 +4584,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>239</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4333,7 +4608,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4348,31 +4623,29 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>20</v>
       </c>
@@ -4381,10 +4654,10 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
@@ -4393,20 +4666,18 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>217</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
       </c>
@@ -4430,29 +4701,31 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4467,16 +4740,16 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>20</v>
+        <v>248</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
@@ -4484,21 +4757,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4510,22 +4783,20 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>110</v>
+        <v>251</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q23" t="s" s="2">
-        <v>248</v>
-      </c>
+      <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
         <v>20</v>
       </c>
@@ -4545,37 +4816,37 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="Z23" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>245</v>
-      </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
@@ -4584,16 +4855,16 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>254</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>20</v>
@@ -4601,102 +4872,96 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>20</v>
+        <v>258</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="P24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q24" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="R24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>255</v>
-      </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
@@ -4708,10 +4973,10 @@
         <v>262</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>20</v>
+        <v>263</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
@@ -4720,26 +4985,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
@@ -4748,18 +5013,20 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>217</v>
+        <v>148</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4783,11 +5050,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4805,7 +5074,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4814,33 +5083,33 @@
         <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>271</v>
+        <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AN25" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="26" hidden="true">
-      <c r="A26" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="B26" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4848,30 +5117,32 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>278</v>
+        <v>110</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4896,13 +5167,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>20</v>
+        <v>279</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4920,10 +5191,10 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>90</v>
@@ -4932,62 +5203,62 @@
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>20</v>
+        <v>281</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>282</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>20</v>
+        <v>283</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>20</v>
+        <v>284</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>137</v>
+        <v>286</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>139</v>
+        <v>288</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5013,55 +5284,55 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>20</v>
+        <v>290</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AC27" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>287</v>
-      </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>20</v>
+        <v>291</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>20</v>
+        <v>293</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -5069,46 +5340,46 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -5132,31 +5403,29 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5165,35 +5434,37 @@
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>271</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AM28" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" hidden="true">
-      <c r="A29" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C29" s="2"/>
+      <c r="C29" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>20</v>
       </c>
@@ -5205,7 +5476,7 @@
         <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>20</v>
@@ -5214,19 +5485,19 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5251,13 +5522,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5275,7 +5546,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5299,32 +5570,34 @@
         <v>304</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>20</v>
+        <v>293</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>20</v>
@@ -5333,19 +5606,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>278</v>
+        <v>190</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5370,13 +5643,11 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>20</v>
+        <v>315</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5394,13 +5665,13 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
@@ -5412,38 +5683,40 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>20</v>
+        <v>293</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="D31" t="s" s="2">
-        <v>314</v>
+        <v>20</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>20</v>
@@ -5452,18 +5725,20 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5487,13 +5762,11 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5511,7 +5784,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5520,7 +5793,7 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>320</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>102</v>
@@ -5529,24 +5802,24 @@
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>20</v>
+        <v>293</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>276</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5569,49 +5842,49 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q32" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="R32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Y32" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
+      <c r="Z32" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="P32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5628,7 +5901,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5643,27 +5916,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>20</v>
+        <v>327</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5671,82 +5944,88 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I33" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M33" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q33" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="R33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AG33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>90</v>
@@ -5758,35 +6037,35 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>336</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>90</v>
@@ -5801,15 +6080,17 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>339</v>
+        <v>295</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5834,13 +6115,11 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>20</v>
+        <v>345</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5858,7 +6137,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5867,37 +6146,37 @@
         <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>20</v>
+        <v>346</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>348</v>
+        <v>20</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5907,22 +6186,22 @@
         <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>349</v>
+        <v>166</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>350</v>
+        <v>167</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>351</v>
+        <v>168</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5973,7 +6252,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>347</v>
+        <v>169</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5985,41 +6264,41 @@
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>353</v>
+        <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>354</v>
+        <v>170</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>355</v>
+        <v>20</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>356</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6028,18 +6307,20 @@
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>358</v>
+        <v>136</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>359</v>
+        <v>137</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6064,43 +6345,43 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>357</v>
+        <v>176</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -6109,25 +6390,27 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>363</v>
+        <v>170</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>364</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="D37" t="s" s="2">
-        <v>366</v>
+        <v>20</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6137,24 +6420,26 @@
         <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6203,56 +6488,56 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>365</v>
+        <v>176</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>20</v>
+        <v>346</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>370</v>
+        <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>374</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>376</v>
+        <v>20</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>20</v>
@@ -6261,18 +6546,20 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6320,13 +6607,13 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
@@ -6335,31 +6622,31 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>384</v>
+        <v>20</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>385</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>387</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6378,18 +6665,20 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6413,13 +6702,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6437,7 +6726,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6452,16 +6741,16 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>393</v>
+        <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>396</v>
+        <v>20</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -6469,14 +6758,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6495,16 +6784,16 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>399</v>
+        <v>295</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6530,13 +6819,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>20</v>
+        <v>384</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>20</v>
+        <v>385</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6554,7 +6843,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6563,33 +6852,33 @@
         <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>20</v>
+        <v>386</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>403</v>
+        <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>405</v>
+        <v>349</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>396</v>
+        <v>20</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>20</v>
+        <v>351</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6600,7 +6889,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6612,16 +6901,18 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>217</v>
+        <v>389</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6645,37 +6936,35 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>409</v>
+        <v>20</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>410</v>
+        <v>20</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>20</v>
+        <v>394</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
@@ -6687,13 +6976,13 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>20</v>
+        <v>387</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>396</v>
+        <v>20</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -6701,12 +6990,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6715,7 +7006,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6727,16 +7018,18 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>414</v>
+        <v>391</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6784,13 +7077,13 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
@@ -6802,13 +7095,13 @@
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>20</v>
+        <v>387</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>396</v>
+        <v>20</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -6816,12 +7109,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>20</v>
       </c>
@@ -6830,7 +7125,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6842,18 +7137,18 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>217</v>
+        <v>401</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>417</v>
+        <v>390</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
       </c>
@@ -6877,11 +7172,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>420</v>
+        <v>20</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6899,13 +7196,13 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>416</v>
+        <v>388</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
@@ -6914,16 +7211,16 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>421</v>
+        <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>422</v>
+        <v>387</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>423</v>
+        <v>395</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>424</v>
+        <v>20</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -6931,12 +7228,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>20</v>
       </c>
@@ -6945,7 +7244,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -6957,18 +7256,18 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>427</v>
+        <v>390</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
       </c>
@@ -7016,13 +7315,13 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>425</v>
+        <v>388</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
@@ -7031,27 +7330,27 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>430</v>
+        <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>431</v>
+        <v>387</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>424</v>
+        <v>20</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7059,28 +7358,28 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>434</v>
+        <v>406</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>435</v>
+        <v>407</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>436</v>
+        <v>408</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7131,13 +7430,13 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
@@ -7146,60 +7445,58 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>437</v>
+        <v>409</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>438</v>
+        <v>410</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>439</v>
+        <v>411</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>20</v>
+        <v>412</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>20</v>
+        <v>413</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7248,13 +7545,13 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
@@ -7263,41 +7560,41 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>447</v>
+        <v>420</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>20</v>
+        <v>422</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>20</v>
+        <v>423</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>20</v>
+        <v>425</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>20</v>
@@ -7306,17 +7603,15 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7353,25 +7648,23 @@
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>20</v>
+        <v>394</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
@@ -7380,41 +7673,43 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>20</v>
+        <v>429</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>20</v>
+        <v>432</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>20</v>
+        <v>433</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>456</v>
+        <v>434</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="D48" t="s" s="2">
-        <v>457</v>
+        <v>425</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>20</v>
@@ -7423,20 +7718,16 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>217</v>
+        <v>436</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>458</v>
+        <v>427</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7460,13 +7751,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>462</v>
+        <v>20</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>463</v>
+        <v>20</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7484,13 +7775,13 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>456</v>
+        <v>424</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
@@ -7499,56 +7790,58 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>20</v>
+        <v>429</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>464</v>
+        <v>431</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>20</v>
+        <v>432</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>465</v>
+        <v>433</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="D49" t="s" s="2">
-        <v>20</v>
+        <v>425</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>467</v>
+        <v>439</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>51</v>
+        <v>427</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>468</v>
+        <v>428</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7599,13 +7892,13 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>466</v>
+        <v>424</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
@@ -7614,31 +7907,33 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>469</v>
+        <v>429</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>321</v>
+        <v>430</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>470</v>
+        <v>431</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>20</v>
+        <v>432</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>471</v>
+        <v>433</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>472</v>
+        <v>440</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="D50" t="s" s="2">
-        <v>20</v>
+        <v>425</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7648,7 +7943,7 @@
         <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>20</v>
@@ -7657,13 +7952,13 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>278</v>
+        <v>442</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>473</v>
+        <v>427</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>474</v>
+        <v>428</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7714,7 +8009,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>472</v>
+        <v>424</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7729,27 +8024,27 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>20</v>
+        <v>429</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>321</v>
+        <v>430</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>475</v>
+        <v>431</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>20</v>
+        <v>432</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>20</v>
+        <v>433</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7760,7 +8055,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7769,20 +8064,18 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7807,37 +8100,35 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>20</v>
+        <v>447</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>20</v>
+        <v>448</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
@@ -7846,23 +8137,1883 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AM55" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Y59" s="2"/>
+      <c r="Z59" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AL67" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="AM51" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO51" t="s" s="2">
+      <c r="AM67" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO67" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO51">
+  <autoFilter ref="A1:AO67">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7872,7 +10023,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI50">
+  <conditionalFormatting sqref="A2:AI66">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$60</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2517" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="548">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T06:46:39+05:30</t>
+    <t>2026-05-19T11:54:54+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -522,10 +522,6 @@
   </si>
   <si>
     <t>internalIdentifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
   </si>
   <si>
     <t>Customer-specific internal identifier whose system SHALL follow the mandated 314e naming convention</t>
@@ -620,7 +616,7 @@
     <t>ServiceRequest.identifier.type</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
+    <t xml:space="preserve">CodeableConcept {http://314e.com/fhir/ig/StructureDefinition/codeableconcept-314e}
 </t>
   </si>
   <si>
@@ -657,10 +653,14 @@
     <t>ServiceRequest.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>Identifier namespace URI or constrained-format internal identifier-system name</t>
+  </si>
+  <si>
+    <t>Establishes the namespace, issuer, or context in which the identifier value is unique.
+Standard identifiers SHOULD use canonical URIs whenever available.
+For customer-specific or internally defined identifier systems,
+the following naming convention SHALL be used:
+[customer]-[ehr]-[ResourceType]-[resource-subtype]-[eleMent]-[SourceSpecificString]-InternalIdentifier</t>
   </si>
   <si>
     <t>Identifier.system is always case sensitive.</t>
@@ -687,13 +687,15 @@
     <t>ServiceRequest.identifier.value</t>
   </si>
   <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>The identifier value</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user
+and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If Identifier.value is populated,
+Identifier.system SHALL also be populated.</t>
   </si>
   <si>
     <t>123456</t>
@@ -714,7 +716,7 @@
     <t>ServiceRequest.identifier.period</t>
   </si>
   <si>
-    <t xml:space="preserve">Period
+    <t xml:space="preserve">Period {http://314e.com/fhir/ig/StructureDefinition/period-314e}
 </t>
   </si>
   <si>
@@ -942,10 +944,6 @@
   </si>
   <si>
     <t>ServiceRequest.category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept {http://314e.com/fhir/ig/StructureDefinition/codeableconcept-314e}
-</t>
   </si>
   <si>
     <t>Operational procedure/service categories</t>
@@ -1238,8 +1236,8 @@
     <t>ServiceRequest.quantity[x]</t>
   </si>
   <si>
-    <t>Quantity
-RatioRange</t>
+    <t>Quantity {http://314e.com/fhir/ig/StructureDefinition/quantity-314e}
+Ratio {http://314e.com/fhir/StructureDefinition/ratio-314e}Range {http://314e.com/fhir/StructureDefinition/range-314e}</t>
   </si>
   <si>
     <t>Service amount</t>
@@ -1251,44 +1249,7 @@
     <t>When ordering a service the number of service items may need to be specified separately from the the service item.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>.quantity</t>
-  </si>
-  <si>
-    <t>ServiceRequest.quantity[x]:quantityQuantity</t>
-  </si>
-  <si>
-    <t>quantityQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity {http://314e.com/fhir/ig/StructureDefinition/quantity-314e}
-</t>
-  </si>
-  <si>
-    <t>ServiceRequest.quantity[x]:quantityRange</t>
-  </si>
-  <si>
-    <t>quantityRange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range {http://314e.com/fhir/StructureDefinition/range-314e}
-</t>
-  </si>
-  <si>
-    <t>ServiceRequest.quantity[x]:quantityRatio</t>
-  </si>
-  <si>
-    <t>quantityRatio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratio {http://314e.com/fhir/StructureDefinition/ratio-314e}
-</t>
   </si>
   <si>
     <t>ServiceRequest.subject</t>
@@ -1358,8 +1319,8 @@
 </t>
   </si>
   <si>
-    <t>dateTime
-PeriodTiming</t>
+    <t>dateTime {http://314e.com/fhir/ig/StructureDefinition/datetime-314e}
+Period {http://314e.com/fhir/ig/StructureDefinition/period-314e}Timing {http://314e.com/fhir/ig/StructureDefinition/timing-314e}</t>
   </si>
   <si>
     <t>(QI) When service should occur</t>
@@ -1383,74 +1344,42 @@
     <t>Procedure.procedureSchedule</t>
   </si>
   <si>
-    <t>ServiceRequest.occurrence[x]:occurrenceDateTime</t>
-  </si>
-  <si>
-    <t>occurrenceDateTime</t>
+    <t>ServiceRequest.asNeeded[x]</t>
+  </si>
+  <si>
+    <t>boolean
+CodeableConcept {http://314e.com/fhir/ig/StructureDefinition/codeableconcept-314e}</t>
+  </si>
+  <si>
+    <t>Preconditions for service</t>
+  </si>
+  <si>
+    <t>If a CodeableConcept is present, it indicates the pre-condition for performing the service.  For example "pain", "on flare-up", etc.</t>
+  </si>
+  <si>
+    <t>A coded concept identifying the pre-condition that should hold prior to performing a procedure.  For example "pain", "on flare-up", etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
+  </si>
+  <si>
+    <t>boolean: precondition.negationInd (inversed - so negationInd = true means asNeeded=false CodeableConcept: precondition.observationEventCriterion[code="Assertion"].value</t>
+  </si>
+  <si>
+    <t>Proposal.prnReason.reason</t>
+  </si>
+  <si>
+    <t>ServiceRequest.authoredOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orderedOn
+</t>
   </si>
   <si>
     <t xml:space="preserve">dateTime {http://314e.com/fhir/ig/StructureDefinition/datetime-314e}
 </t>
   </si>
   <si>
-    <t>ServiceRequest.occurrence[x]:occurrencePeriod</t>
-  </si>
-  <si>
-    <t>occurrencePeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period {http://314e.com/fhir/ig/StructureDefinition/period-314e}
-</t>
-  </si>
-  <si>
-    <t>ServiceRequest.occurrence[x]:occurrenceTiming</t>
-  </si>
-  <si>
-    <t>occurrenceTiming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timing {http://314e.com/fhir/ig/StructureDefinition/timing-314e}
-</t>
-  </si>
-  <si>
-    <t>ServiceRequest.asNeeded[x]</t>
-  </si>
-  <si>
-    <t>boolean
-CodeableConcept</t>
-  </si>
-  <si>
-    <t>Preconditions for service</t>
-  </si>
-  <si>
-    <t>If a CodeableConcept is present, it indicates the pre-condition for performing the service.  For example "pain", "on flare-up", etc.</t>
-  </si>
-  <si>
-    <t>A coded concept identifying the pre-condition that should hold prior to performing a procedure.  For example "pain", "on flare-up", etc.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
-  </si>
-  <si>
-    <t>boolean: precondition.negationInd (inversed - so negationInd = true means asNeeded=false CodeableConcept: precondition.observationEventCriterion[code="Assertion"].value</t>
-  </si>
-  <si>
-    <t>Proposal.prnReason.reason</t>
-  </si>
-  <si>
-    <t>ServiceRequest.asNeeded[x]:asNeededCodeableConcept</t>
-  </si>
-  <si>
-    <t>asNeededCodeableConcept</t>
-  </si>
-  <si>
-    <t>ServiceRequest.authoredOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderedOn
-</t>
-  </si>
-  <si>
     <t>(QI) Date request signed</t>
   </si>
   <si>
@@ -1571,6 +1500,10 @@
   </si>
   <si>
     <t>ServiceRequest.locationCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
   </si>
   <si>
     <t>Requested location</t>
@@ -2128,12 +2061,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO67"/>
+  <dimension ref="A1:AO60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.484375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.5390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="30.87890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.57421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="38.546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -3494,13 +3427,13 @@
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N12" t="s" s="2">
         <v>151</v>
@@ -3585,10 +3518,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3611,13 +3544,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3668,7 +3601,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3689,7 +3622,7 @@
         <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>20</v>
@@ -3700,10 +3633,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3732,7 +3665,7 @@
         <v>137</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>139</v>
@@ -3773,10 +3706,10 @@
         <v>20</v>
       </c>
       <c r="AB14" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AC14" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>20</v>
@@ -3785,7 +3718,7 @@
         <v>153</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3806,7 +3739,7 @@
         <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>20</v>
@@ -3817,10 +3750,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3846,16 +3779,16 @@
         <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3880,31 +3813,31 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3925,7 +3858,7 @@
         <v>133</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>20</v>
@@ -3936,10 +3869,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3962,19 +3895,19 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3999,31 +3932,31 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4041,10 +3974,10 @@
         <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>20</v>
@@ -4055,10 +3988,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4084,16 +4017,16 @@
         <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -4106,43 +4039,43 @@
         <v>20</v>
       </c>
       <c r="T17" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4160,10 +4093,10 @@
         <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>20</v>
@@ -4174,10 +4107,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4200,16 +4133,16 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4223,43 +4156,43 @@
         <v>20</v>
       </c>
       <c r="T18" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4277,10 +4210,10 @@
         <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>20</v>
@@ -4291,10 +4224,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4317,13 +4250,13 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4374,7 +4307,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4392,10 +4325,10 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>20</v>
@@ -4406,10 +4339,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4432,16 +4365,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4491,7 +4424,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4509,10 +4442,10 @@
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>20</v>
@@ -4523,10 +4456,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4549,16 +4482,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4608,7 +4541,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4623,13 +4556,13 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AM21" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
@@ -4640,10 +4573,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4669,13 +4602,13 @@
         <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4725,7 +4658,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4740,13 +4673,13 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
@@ -4757,14 +4690,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4783,13 +4716,13 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4840,7 +4773,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4855,13 +4788,13 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
@@ -4872,14 +4805,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4898,13 +4831,13 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4955,7 +4888,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4970,13 +4903,13 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
@@ -4987,14 +4920,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5016,16 +4949,16 @@
         <v>148</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5074,7 +5007,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5089,13 +5022,13 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>20</v>
@@ -5106,10 +5039,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5135,13 +5068,13 @@
         <v>110</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5167,14 +5100,14 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>279</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
       </c>
@@ -5191,7 +5124,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -5206,27 +5139,27 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5252,13 +5185,13 @@
         <v>110</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5284,14 +5217,14 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>290</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
       </c>
@@ -5308,7 +5241,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>90</v>
@@ -5323,16 +5256,16 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>133</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -5340,10 +5273,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5366,19 +5299,19 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5403,13 +5336,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5425,7 +5358,7 @@
         <v>153</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5443,13 +5376,13 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -5457,13 +5390,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>20</v>
@@ -5485,19 +5418,19 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>295</v>
+        <v>189</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5522,13 +5455,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5546,7 +5479,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5564,13 +5497,13 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5578,13 +5511,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>20</v>
@@ -5606,19 +5539,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5643,11 +5576,11 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5665,7 +5598,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5683,13 +5616,13 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -5697,13 +5630,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>20</v>
@@ -5725,19 +5658,19 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5762,11 +5695,11 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5784,7 +5717,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5802,13 +5735,13 @@
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -5816,10 +5749,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5845,10 +5778,10 @@
         <v>110</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5856,35 +5789,35 @@
         <v>20</v>
       </c>
       <c r="Q32" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="R32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="R32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>326</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5901,7 +5834,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5916,16 +5849,16 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5933,10 +5866,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5959,26 +5892,26 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="P33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q33" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="O33" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="P33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q33" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="R33" t="s" s="2">
         <v>20</v>
       </c>
@@ -6022,7 +5955,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6037,13 +5970,13 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -6054,14 +5987,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6080,16 +6013,16 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>295</v>
+        <v>189</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6115,11 +6048,11 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -6137,7 +6070,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6146,33 +6079,33 @@
         <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6195,13 +6128,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6252,7 +6185,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6273,7 +6206,7 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -6284,10 +6217,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6316,7 +6249,7 @@
         <v>137</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>139</v>
@@ -6357,10 +6290,10 @@
         <v>20</v>
       </c>
       <c r="AB36" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AC36" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>20</v>
@@ -6369,7 +6302,7 @@
         <v>153</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6390,7 +6323,7 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
@@ -6401,13 +6334,13 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B37" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="C37" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>20</v>
@@ -6429,16 +6362,16 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6488,7 +6421,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6497,7 +6430,7 @@
         <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>141</v>
@@ -6506,10 +6439,10 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
@@ -6520,10 +6453,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6546,19 +6479,19 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6607,7 +6540,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6625,10 +6558,10 @@
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6639,10 +6572,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6665,19 +6598,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6726,7 +6659,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6744,10 +6677,10 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
@@ -6758,14 +6691,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6784,16 +6717,16 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>295</v>
+        <v>189</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6819,13 +6752,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6843,7 +6776,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6852,7 +6785,7 @@
         <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>102</v>
@@ -6861,24 +6794,24 @@
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6901,17 +6834,17 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6948,17 +6881,19 @@
         <v>20</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>394</v>
+        <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6976,10 +6911,10 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -6988,28 +6923,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
@@ -7018,18 +6951,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
-        <v>392</v>
-      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -7077,10 +7008,10 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>90</v>
@@ -7092,33 +7023,31 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>20</v>
+        <v>396</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>20</v>
+        <v>399</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>20</v>
+        <v>400</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>20</v>
+        <v>402</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7128,7 +7057,7 @@
         <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>20</v>
@@ -7137,18 +7066,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>392</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
       </c>
@@ -7196,7 +7123,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7211,33 +7138,31 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>20</v>
+        <v>406</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>20</v>
+        <v>409</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>20</v>
+        <v>410</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>20</v>
+        <v>412</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7247,7 +7172,7 @@
         <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>20</v>
@@ -7256,18 +7181,16 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>392</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>20</v>
       </c>
@@ -7315,7 +7238,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7330,27 +7253,27 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>20</v>
+        <v>416</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>387</v>
+        <v>417</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>20</v>
+        <v>419</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>20</v>
+        <v>420</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7358,13 +7281,13 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>20</v>
@@ -7373,13 +7296,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7406,13 +7329,13 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>20</v>
+        <v>425</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>20</v>
+        <v>426</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -7430,10 +7353,10 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>90</v>
@@ -7445,31 +7368,31 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>409</v>
+        <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>410</v>
+        <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>412</v>
+        <v>20</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>413</v>
+        <v>428</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7488,13 +7411,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7545,7 +7468,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7560,31 +7483,31 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>423</v>
+        <v>438</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7603,15 +7526,17 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7648,17 +7573,19 @@
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AC47" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>394</v>
+        <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7673,33 +7600,31 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>433</v>
+        <v>449</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7709,7 +7634,7 @@
         <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>20</v>
@@ -7718,15 +7643,17 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>436</v>
+        <v>189</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7751,13 +7678,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>20</v>
+        <v>455</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7775,7 +7702,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7790,43 +7717,41 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>433</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>20</v>
@@ -7835,15 +7760,17 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>427</v>
+        <v>464</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7892,13 +7819,13 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>424</v>
+        <v>461</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
@@ -7907,43 +7834,41 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>429</v>
+        <v>467</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>430</v>
+        <v>468</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>431</v>
+        <v>469</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>433</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>425</v>
+        <v>20</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>20</v>
@@ -7952,13 +7877,13 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>442</v>
+        <v>471</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>427</v>
+        <v>472</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>428</v>
+        <v>473</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7985,13 +7910,13 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>20</v>
+        <v>474</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>20</v>
+        <v>475</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -8009,13 +7934,13 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>424</v>
+        <v>470</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
@@ -8024,27 +7949,27 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>429</v>
+        <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>430</v>
+        <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>431</v>
+        <v>476</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>433</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8055,7 +7980,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -8067,13 +7992,13 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>444</v>
+        <v>478</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>446</v>
+        <v>479</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8100,35 +8025,37 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>447</v>
+        <v>20</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>448</v>
+        <v>20</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AC51" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
@@ -8143,25 +8070,23 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>449</v>
+        <v>480</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>20</v>
+        <v>460</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>450</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>451</v>
+        <v>481</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>20</v>
       </c>
@@ -8170,7 +8095,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -8182,15 +8107,17 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>295</v>
+        <v>189</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>445</v>
+        <v>482</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8215,13 +8142,11 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -8239,13 +8164,13 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>443</v>
+        <v>481</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
@@ -8254,41 +8179,41 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>20</v>
+        <v>486</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>20</v>
+        <v>487</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>449</v>
+        <v>488</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>20</v>
+        <v>489</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>450</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>454</v>
+        <v>20</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>20</v>
@@ -8297,15 +8222,17 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>436</v>
+        <v>491</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>455</v>
+        <v>492</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8354,13 +8281,13 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
@@ -8369,60 +8296,58 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>457</v>
+        <v>495</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>458</v>
+        <v>496</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>459</v>
+        <v>497</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>460</v>
+        <v>489</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>461</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>462</v>
+        <v>498</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>462</v>
+        <v>498</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>463</v>
+        <v>20</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>464</v>
+        <v>499</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>465</v>
+        <v>500</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>501</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8471,13 +8396,13 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>462</v>
+        <v>498</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
@@ -8486,38 +8411,38 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>468</v>
+        <v>502</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>471</v>
+        <v>20</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>472</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8526,19 +8451,19 @@
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>295</v>
+        <v>507</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>475</v>
+        <v>508</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>476</v>
+        <v>509</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>477</v>
+        <v>510</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8564,13 +8489,13 @@
         <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>478</v>
+        <v>20</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>479</v>
+        <v>20</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -8588,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
@@ -8603,16 +8528,16 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>480</v>
+        <v>511</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>481</v>
+        <v>512</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>482</v>
+        <v>513</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>483</v>
+        <v>20</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -8620,14 +8545,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>484</v>
+        <v>514</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>484</v>
+        <v>514</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>485</v>
+        <v>20</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8646,16 +8571,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>486</v>
+        <v>515</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>487</v>
+        <v>516</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>488</v>
+        <v>517</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>489</v>
+        <v>518</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8705,7 +8630,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>484</v>
+        <v>514</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8720,16 +8645,16 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>490</v>
+        <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>491</v>
+        <v>519</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>492</v>
+        <v>520</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>483</v>
+        <v>20</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -8737,14 +8662,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>493</v>
+        <v>521</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>493</v>
+        <v>521</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>20</v>
+        <v>522</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8763,16 +8688,20 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>494</v>
+        <v>523</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
       </c>
@@ -8796,13 +8725,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>496</v>
+        <v>527</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>497</v>
+        <v>528</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8820,7 +8749,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>493</v>
+        <v>521</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8838,24 +8767,24 @@
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>20</v>
+        <v>519</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>498</v>
+        <v>529</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>483</v>
+        <v>20</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>20</v>
+        <v>530</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8875,16 +8804,16 @@
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>494</v>
+        <v>51</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8935,7 +8864,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8950,27 +8879,27 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>20</v>
+        <v>534</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>20</v>
+        <v>385</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>502</v>
+        <v>535</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>483</v>
+        <v>20</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>20</v>
+        <v>536</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>503</v>
+        <v>537</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>503</v>
+        <v>537</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8981,7 +8910,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -8993,17 +8922,15 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>295</v>
+        <v>165</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>504</v>
+        <v>538</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9028,11 +8955,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y59" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z59" t="s" s="2">
-        <v>507</v>
+        <v>20</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -9050,13 +8979,13 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>503</v>
+        <v>537</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
@@ -9065,16 +8994,16 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>508</v>
+        <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>509</v>
+        <v>385</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>511</v>
+        <v>20</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -9082,10 +9011,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>512</v>
+        <v>541</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>512</v>
+        <v>541</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9105,19 +9034,19 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>513</v>
+        <v>542</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>514</v>
+        <v>543</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>515</v>
+        <v>544</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>516</v>
+        <v>545</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9167,7 +9096,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>512</v>
+        <v>541</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9182,838 +9111,23 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>517</v>
+        <v>546</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>518</v>
+        <v>133</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>511</v>
+        <v>20</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO67" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO67">
+  <autoFilter ref="A1:AO60">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10023,7 +9137,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI66">
+  <conditionalFormatting sqref="A2:AI59">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:54:54+05:30</t>
+    <t>2026-05-25T12:07:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:48:22+05:30</t>
+    <t>2026-05-26T12:06:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -321,7 +321,7 @@
     <t>ServiceRequest.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -810,7 +810,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|MedicationRequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -836,7 +836,7 @@
 priorrenewed order</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/servicerequest-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1255,7 +1255,7 @@
     <t>ServiceRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1287,7 +1287,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1408,7 +1408,7 @@
 orderer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-practitioner|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-practitionerrole|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-organization|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-relatedperson|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-device|http://hl7.org/fhir/us/core/StructureDefinition/us-core-implantable-device) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://hl7.org/fhir/us/core/StructureDefinition/us-core-implantable-device) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1477,7 +1477,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|HealthcareService|Patient|Device|RelatedPerson) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/healthcareservice-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1564,7 +1564,7 @@
     <t>ServiceRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-condition-encounter-diagnosis|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-condition-problems-health-concerns|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-diagnosticreport-note|http://hl7.org/fhir/us/core/StructureDefinition/us-core-documentreference|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-simple-observation) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1589,7 +1589,7 @@
     <t>ServiceRequest.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Coverage|ClaimResponse) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/coverage-314e|ClaimResponse) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1615,7 +1615,7 @@
 AOE</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(Resource|http://314e.com/fhir/StructureDefinition/account-314e|http://314e.com/fhir/StructureDefinition/allergyintolerance-314e|http://314e.com/fhir/StructureDefinition/appointment-314e|http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/clinicalimpression-314e|http://314e.com/fhir/StructureDefinition/communicationrequest-314e|http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/contract-314e|http://314e.com/fhir/StructureDefinition/coverage-314e|http://314e.com/fhir/StructureDefinition/detectedissue-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/devicerequest-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e|http://314e.com/fhir/StructureDefinition/encounter-314e|http://314e.com/fhir/StructureDefinition/endpoint-314e|http://314e.com/fhir/StructureDefinition/episodeofcare-314e|http://314e.com/fhir/StructureDefinition/goal-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/healthcareservice-314e|http://314e.com/fhir/StructureDefinition/imagingstudy-314e|http://314e.com/fhir/StructureDefinition/immunization-314e|http://314e.com/fhir/StructureDefinition/immunizationevaluation-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e|http://314e.com/fhir/StructureDefinition/location-314e|http://314e.com/fhir/StructureDefinition/media-314e|http://314e.com/fhir/StructureDefinition/medication-314e|http://314e.com/fhir/StructureDefinition/medicationadministration-314e|http://314e.com/fhir/StructureDefinition/medicationdispense-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/molecularsequence-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/procedure-314e|http://314e.com/fhir/StructureDefinition/questionnaireresponse-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/requestgroup-314e|http://314e.com/fhir/StructureDefinition/schedule-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e|http://314e.com/fhir/StructureDefinition/slot-314e|http://314e.com/fhir/StructureDefinition/specimen-314e|http://314e.com/fhir/StructureDefinition/substance-314e|http://314e.com/fhir/StructureDefinition/task-314e|http://314e.com/fhir/StructureDefinition/visionprescription-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1640,7 +1640,7 @@
     <t>ServiceRequest.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/specimen-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-servicerequest-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2293" uniqueCount="555">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -440,33 +440,58 @@
     <t>ServiceRequest.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:cosigner</t>
+  </si>
+  <si>
+    <t>cosigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/resource-cosigner}
+</t>
+  </si>
+  <si>
+    <t>Individual who co-signed or verified this service request</t>
+  </si>
+  <si>
+    <t>Identifies an individual who reviewed, verified, or co-signed the associated
+clinical document, note, order, or healthcare record, alongside the primary author or requester.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>ServiceRequest.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>ServiceRequest.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -474,6 +499,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -498,9 +526,6 @@
   <si>
     <t xml:space="preserve">pattern:$this}
 </t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Request.identifier</t>
@@ -564,11 +589,10 @@
     <t>ServiceRequest.identifier.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
@@ -2061,7 +2085,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO60"/>
+  <dimension ref="A1:AO61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.5390625" customWidth="true" bestFit="true"/>
@@ -3055,7 +3079,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3074,17 +3098,15 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>139</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>20</v>
@@ -3121,16 +3143,14 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>140</v>
@@ -3154,7 +3174,7 @@
         <v>20</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>20</v>
@@ -3168,43 +3188,41 @@
         <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>20</v>
       </c>
@@ -3252,7 +3270,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3261,7 +3279,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>141</v>
@@ -3273,7 +3291,7 @@
         <v>20</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>20</v>
@@ -3284,14 +3302,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3304,24 +3322,26 @@
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O11" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
       </c>
@@ -3357,17 +3377,19 @@
         <v>20</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AC11" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3379,34 +3401,32 @@
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>157</v>
+        <v>20</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>158</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>20</v>
       </c>
@@ -3427,16 +3447,16 @@
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3474,19 +3494,17 @@
         <v>20</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3501,29 +3519,31 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
       </c>
@@ -3532,7 +3552,7 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -3541,18 +3561,20 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3601,34 +3623,34 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>20</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" hidden="true">
@@ -3640,14 +3662,14 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3659,17 +3681,15 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3706,16 +3726,16 @@
         <v>20</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>175</v>
@@ -3724,13 +3744,13 @@
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>20</v>
@@ -3739,7 +3759,7 @@
         <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>20</v>
@@ -3750,46 +3770,44 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>20</v>
       </c>
@@ -3813,52 +3831,52 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Y15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>20</v>
@@ -3869,10 +3887,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3889,25 +3907,25 @@
         <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3932,13 +3950,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3956,7 +3974,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3974,10 +3992,10 @@
         <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>198</v>
+        <v>133</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>20</v>
@@ -3988,10 +4006,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4014,19 +4032,19 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>104</v>
+        <v>196</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -4039,7 +4057,7 @@
         <v>20</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>20</v>
@@ -4051,13 +4069,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>20</v>
+        <v>201</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>20</v>
+        <v>203</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -4075,7 +4093,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4093,10 +4111,10 @@
         <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>20</v>
@@ -4107,10 +4125,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4133,18 +4151,20 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="O18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>20</v>
       </c>
@@ -4156,7 +4176,7 @@
         <v>20</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>20</v>
@@ -4192,7 +4212,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4210,10 +4230,10 @@
         <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>20</v>
@@ -4224,10 +4244,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4250,15 +4270,17 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4271,7 +4293,7 @@
         <v>20</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>20</v>
@@ -4307,7 +4329,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4325,10 +4347,10 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>20</v>
@@ -4339,10 +4361,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4365,17 +4387,15 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>231</v>
-      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4424,7 +4444,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4442,10 +4462,10 @@
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>20</v>
@@ -4456,10 +4476,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4470,7 +4490,7 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4482,16 +4502,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4541,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -4556,13 +4576,13 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AM21" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
@@ -4573,10 +4593,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4599,7 +4619,7 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>104</v>
+        <v>243</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>244</v>
@@ -4658,7 +4678,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4676,10 +4696,10 @@
         <v>247</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
@@ -4690,14 +4710,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4716,7 +4736,7 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>250</v>
+        <v>104</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>251</v>
@@ -4724,7 +4744,9 @@
       <c r="M23" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N23" s="2"/>
+      <c r="N23" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4773,7 +4795,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4788,13 +4810,13 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
@@ -4805,14 +4827,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4831,13 +4853,13 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4888,7 +4910,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4903,13 +4925,13 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
@@ -4920,21 +4942,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4946,7 +4968,7 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>148</v>
+        <v>265</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>266</v>
@@ -4954,12 +4976,8 @@
       <c r="M25" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N25" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>269</v>
-      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -5007,13 +5025,13 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -5022,61 +5040,63 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" hidden="true">
+      <c r="A26" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AM25" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>273</v>
-      </c>
       <c r="B26" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>20</v>
+        <v>272</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
@@ -5100,13 +5120,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>182</v>
+        <v>20</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>278</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -5124,10 +5144,10 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>90</v>
@@ -5139,27 +5159,27 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>281</v>
-      </c>
       <c r="AN26" t="s" s="2">
-        <v>282</v>
+        <v>20</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>283</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5185,13 +5205,13 @@
         <v>110</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5217,13 +5237,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -5241,7 +5261,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>90</v>
@@ -5256,27 +5276,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AM27" t="s" s="2">
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AN27" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" hidden="true">
-      <c r="A28" t="s" s="2">
-        <v>293</v>
-      </c>
       <c r="B28" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5287,32 +5307,30 @@
         <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>91</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>297</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -5336,35 +5354,37 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>298</v>
+        <v>189</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AC28" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
@@ -5373,37 +5393,35 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>20</v>
+        <v>297</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>301</v>
+        <v>133</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>81</v>
@@ -5418,19 +5436,19 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5455,31 +5473,29 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>182</v>
+        <v>305</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>308</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5497,13 +5513,13 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5511,23 +5527,23 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>91</v>
@@ -5539,19 +5555,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5576,11 +5592,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5598,7 +5616,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5616,13 +5634,13 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -5630,20 +5648,20 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>90</v>
@@ -5658,19 +5676,19 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5695,11 +5713,11 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5717,7 +5735,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5735,26 +5753,28 @@
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="D32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5766,7 +5786,7 @@
         <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>20</v>
@@ -5775,22 +5795,24 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q32" t="s" s="2">
-        <v>322</v>
-      </c>
+      <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5810,13 +5832,11 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5834,13 +5854,13 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
@@ -5849,16 +5869,16 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>325</v>
+        <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5866,10 +5886,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5886,59 +5906,55 @@
         <v>20</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q33" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="R33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Y33" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="Z33" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M33" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="P33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q33" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="R33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5955,7 +5971,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5970,65 +5986,69 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>338</v>
-      </c>
       <c r="B34" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I34" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>189</v>
+        <v>337</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="P34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q34" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="O34" s="2"/>
-      <c r="P34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
         <v>20</v>
       </c>
@@ -6048,11 +6068,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="Y34" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z34" t="s" s="2">
-        <v>343</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -6070,7 +6092,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6079,64 +6101,66 @@
         <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>344</v>
+        <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="35" hidden="true">
-      <c r="A35" t="s" s="2">
-        <v>350</v>
-      </c>
       <c r="B35" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>20</v>
+        <v>346</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>166</v>
+        <v>347</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6161,13 +6185,11 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>20</v>
+        <v>350</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -6185,7 +6207,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>168</v>
+        <v>345</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6194,44 +6216,44 @@
         <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>20</v>
+        <v>351</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>20</v>
+        <v>352</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>20</v>
+        <v>353</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>169</v>
+        <v>354</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>20</v>
+        <v>356</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6243,17 +6265,15 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6290,16 +6310,16 @@
         <v>20</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>175</v>
@@ -6308,13 +6328,13 @@
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -6323,7 +6343,7 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
@@ -6334,23 +6354,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6362,16 +6380,16 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>354</v>
+        <v>135</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>355</v>
+        <v>179</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>356</v>
+        <v>180</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>357</v>
+        <v>152</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6409,19 +6427,19 @@
         <v>20</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6430,7 +6448,7 @@
         <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>344</v>
+        <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>141</v>
@@ -6439,10 +6457,10 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>358</v>
+        <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>359</v>
+        <v>176</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
@@ -6453,12 +6471,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C38" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="B38" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6467,7 +6487,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6476,7 +6496,7 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>361</v>
@@ -6490,9 +6510,7 @@
       <c r="N38" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="O38" t="s" s="2">
-        <v>365</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6540,7 +6558,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>366</v>
+        <v>182</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6549,19 +6567,19 @@
         <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>20</v>
+        <v>351</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6572,10 +6590,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6586,7 +6604,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6598,19 +6616,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>165</v>
+        <v>368</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6659,13 +6677,13 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
@@ -6677,10 +6695,10 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
@@ -6691,21 +6709,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6717,18 +6735,20 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N40" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6752,13 +6772,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>298</v>
+        <v>20</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>382</v>
+        <v>20</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>383</v>
+        <v>20</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6776,16 +6796,16 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>384</v>
+        <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>102</v>
@@ -6794,35 +6814,35 @@
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>347</v>
+        <v>383</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>349</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>20</v>
+        <v>385</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6834,18 +6854,18 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>390</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6869,13 +6889,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>20</v>
+        <v>305</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>20</v>
+        <v>389</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>20</v>
+        <v>390</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6893,16 +6913,16 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>102</v>
@@ -6911,24 +6931,24 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>391</v>
+        <v>354</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>20</v>
+        <v>356</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6936,13 +6956,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
@@ -6951,16 +6971,18 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -7008,10 +7030,10 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>90</v>
@@ -7023,35 +7045,35 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>396</v>
+        <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>398</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>399</v>
+        <v>20</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>400</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>402</v>
+        <v>20</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>90</v>
@@ -7066,13 +7088,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7123,10 +7145,10 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>90</v>
@@ -7138,31 +7160,31 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>410</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7181,13 +7203,13 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7238,7 +7260,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7253,31 +7275,31 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AM44" t="s" s="2">
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AN44" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>421</v>
-      </c>
       <c r="B45" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>20</v>
+        <v>419</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7287,7 +7309,7 @@
         <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>20</v>
@@ -7296,13 +7318,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7329,13 +7351,13 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>298</v>
+        <v>20</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>425</v>
+        <v>20</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>426</v>
+        <v>20</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -7353,7 +7375,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7368,31 +7390,31 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>20</v>
+        <v>423</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>20</v>
+        <v>424</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AN45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO45" t="s" s="2">
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
         <v>428</v>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>429</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>430</v>
+        <v>20</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7402,7 +7424,7 @@
         <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>20</v>
@@ -7411,13 +7433,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7444,13 +7466,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>20</v>
+        <v>305</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>20</v>
+        <v>432</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>20</v>
+        <v>433</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7468,7 +7490,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7483,31 +7505,31 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>438</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7526,17 +7548,15 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7585,7 +7605,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7600,31 +7620,31 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AL47" t="s" s="2">
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AM47" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="48" hidden="true">
-      <c r="A48" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="B48" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7634,7 +7654,7 @@
         <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>20</v>
@@ -7643,16 +7663,16 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>189</v>
+        <v>448</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7678,13 +7698,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>298</v>
+        <v>20</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>455</v>
+        <v>20</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>456</v>
+        <v>20</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7702,7 +7722,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7717,38 +7737,38 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>20</v>
+        <v>456</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7760,16 +7780,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>463</v>
+        <v>196</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7795,13 +7815,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>20</v>
+        <v>305</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>20</v>
+        <v>462</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>20</v>
+        <v>463</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7819,13 +7839,13 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
@@ -7834,16 +7854,16 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -7851,14 +7871,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>20</v>
+        <v>469</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7877,15 +7897,17 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7910,13 +7932,13 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>298</v>
+        <v>20</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>474</v>
+        <v>20</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>475</v>
+        <v>20</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -7934,7 +7956,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7949,16 +7971,16 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>20</v>
+        <v>474</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>20</v>
+        <v>475</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>476</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -7995,10 +8017,10 @@
         <v>478</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8025,13 +8047,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>20</v>
+        <v>305</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>20</v>
+        <v>481</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>20</v>
+        <v>482</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -8070,10 +8092,10 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8081,10 +8103,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8107,17 +8129,15 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>189</v>
+        <v>485</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8142,11 +8162,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>485</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -8164,7 +8186,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8179,16 +8201,16 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>486</v>
+        <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AM52" t="s" s="2">
-        <v>488</v>
-      </c>
       <c r="AN52" t="s" s="2">
-        <v>489</v>
+        <v>467</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8196,10 +8218,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8222,16 +8244,16 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8257,13 +8279,11 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>20</v>
+        <v>492</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8281,7 +8301,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8296,16 +8316,16 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8313,10 +8333,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8336,18 +8356,20 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8396,7 +8418,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8420,7 +8442,7 @@
         <v>504</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>20</v>
+        <v>496</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -8435,7 +8457,7 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>506</v>
+        <v>20</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8454,17 +8476,15 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>510</v>
-      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8528,13 +8548,13 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>20</v>
@@ -8545,14 +8565,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>20</v>
+        <v>513</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8568,19 +8588,19 @@
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8630,7 +8650,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8645,7 +8665,7 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>20</v>
+        <v>518</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>519</v>
@@ -8669,7 +8689,7 @@
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>522</v>
+        <v>20</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8688,7 +8708,7 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>189</v>
+        <v>522</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>523</v>
@@ -8699,9 +8719,7 @@
       <c r="N57" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="O57" t="s" s="2">
-        <v>526</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>20</v>
       </c>
@@ -8725,13 +8743,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>298</v>
+        <v>20</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>527</v>
+        <v>20</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>528</v>
+        <v>20</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8767,28 +8785,28 @@
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>530</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>20</v>
+        <v>529</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8804,19 +8822,23 @@
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L58" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="M58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>20</v>
       </c>
@@ -8840,13 +8862,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>20</v>
+        <v>305</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>20</v>
+        <v>534</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>20</v>
+        <v>535</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -8864,7 +8886,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8879,27 +8901,27 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>534</v>
+        <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>385</v>
+        <v>526</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8910,7 +8932,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -8919,16 +8941,16 @@
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>165</v>
+        <v>539</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>538</v>
+        <v>51</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8979,13 +9001,13 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
@@ -8994,27 +9016,27 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>20</v>
+        <v>541</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>20</v>
+        <v>543</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9025,7 +9047,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -9034,20 +9056,18 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>542</v>
+        <v>172</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9096,13 +9116,13 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
@@ -9111,10 +9131,10 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>546</v>
+        <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>133</v>
+        <v>392</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>547</v>
@@ -9126,8 +9146,125 @@
         <v>20</v>
       </c>
     </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AO60">
+  <autoFilter ref="A1:AO61">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9137,7 +9274,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI59">
+  <conditionalFormatting sqref="A2:AI60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
